--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="110">
   <si>
     <t>Mat</t>
   </si>
@@ -85,328 +85,268 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
     <t>ESPIRITU</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
   </si>
   <si>
     <t>VENTURA</t>
   </si>
   <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CID</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>BUENO</t>
-  </si>
-  <si>
-    <t>COLOTL</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CUEVAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
     <t>TEQUIHUATLE</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
   </si>
   <si>
     <t>EVARISTO</t>
   </si>
   <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
+    <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>AISHA NAOMI</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>MARCOS URIEL</t>
-  </si>
-  <si>
-    <t>ADAN</t>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>DIANA ARELI</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>EDGAR DANIEL</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAHIR</t>
   </si>
   <si>
     <t>OMAR ALDAIR</t>
   </si>
   <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
+    <t>JAROMI YAJAIRA</t>
+  </si>
+  <si>
+    <t>EDGAR RAMSES</t>
+  </si>
+  <si>
+    <t>XIMENA MICHELL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
   </si>
   <si>
     <t>ALDAIR ALAN</t>
   </si>
   <si>
-    <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>JORGE LUIS</t>
-  </si>
-  <si>
-    <t>ALMA RUBI</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>ALEXIS MANUEL</t>
-  </si>
-  <si>
-    <t>JOSE ABRAHAM</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>JOSE MATEO</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>CRISTAL</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
-  </si>
-  <si>
-    <t>JAROMI YAJAIRA</t>
-  </si>
-  <si>
-    <t>EDGAR RAMSES</t>
-  </si>
-  <si>
-    <t>XIMENA MICHELL</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
     <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
   </si>
 </sst>
 </file>
@@ -1002,16 +942,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>70.97</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1025,16 +968,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>91.43000000000001</v>
+      </c>
+      <c r="H3">
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1048,16 +994,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>11</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>52.38</v>
+      </c>
+      <c r="H4">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1071,16 +1020,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>64.86</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1094,16 +1046,19 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>63.33</v>
+      </c>
+      <c r="H6">
+        <v>5.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1117,16 +1072,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>84.38</v>
+      </c>
+      <c r="H7">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -1182,16 +1140,16 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>35.48</v>
+        <v>70.97</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1208,16 +1166,16 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>97.14</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1243,7 +1201,7 @@
         <v>52.38</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1269,7 +1227,7 @@
         <v>67.56999999999999</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1286,16 +1244,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>53.33</v>
+        <v>63.33</v>
       </c>
       <c r="H6">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1321,7 +1279,7 @@
         <v>96.88</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -1331,7 +1289,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1363,16 +1321,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920011</v>
+        <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1392,10 +1350,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1409,16 +1367,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920025</v>
+        <v>20330051920021</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1432,22 +1390,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920035</v>
+        <v>20330051920241</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1455,16 +1413,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920337</v>
+        <v>20330051920336</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1478,16 +1436,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330050470596</v>
+        <v>20330051920337</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1507,10 +1465,10 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1530,10 +1488,10 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1553,10 +1511,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1570,16 +1528,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920174</v>
+        <v>20330051920168</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1593,16 +1551,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920178</v>
+        <v>20330051920174</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1616,16 +1574,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920182</v>
+        <v>20330051920178</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1639,16 +1597,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920388</v>
+        <v>20330051920182</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1662,22 +1620,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920097</v>
+        <v>20330051920388</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1691,10 +1649,10 @@
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1708,16 +1666,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920004</v>
+        <v>20330051920362</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1731,16 +1689,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920007</v>
+        <v>20330051920011</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1754,16 +1712,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920362</v>
+        <v>20330051920012</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1777,16 +1735,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920009</v>
+        <v>20330051920060</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1800,16 +1758,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920012</v>
+        <v>20330051920033</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1823,22 +1781,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920014</v>
+        <v>20330051920340</v>
       </c>
       <c r="B22" t="s">
         <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1846,22 +1804,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920026</v>
+        <v>20330051920381</v>
       </c>
       <c r="B23" t="s">
         <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D23" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1869,22 +1827,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920060</v>
+        <v>20330051920347</v>
       </c>
       <c r="B24" t="s">
         <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="D24" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1892,22 +1850,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920028</v>
+        <v>20330051920349</v>
       </c>
       <c r="B25" t="s">
         <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1915,22 +1873,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920029</v>
+        <v>19330050470596</v>
       </c>
       <c r="B26" t="s">
         <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1938,22 +1896,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920033</v>
+        <v>20330051920180</v>
       </c>
       <c r="B27" t="s">
         <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1961,22 +1919,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920037</v>
+        <v>20330051920373</v>
       </c>
       <c r="B28" t="s">
         <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1984,22 +1942,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920340</v>
+        <v>20330051920145</v>
       </c>
       <c r="B29" t="s">
         <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2007,22 +1965,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920381</v>
+        <v>20330051920044</v>
       </c>
       <c r="B30" t="s">
         <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2030,22 +1988,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920347</v>
+        <v>20330051920046</v>
       </c>
       <c r="B31" t="s">
         <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2053,22 +2011,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920349</v>
+        <v>20330051920052</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2076,22 +2034,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920180</v>
+        <v>20330051920096</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D33" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2099,22 +2057,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920373</v>
+        <v>20330051920097</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="D34" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2122,208 +2080,24 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920145</v>
+        <v>20330051920104</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="D35" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>20330051920039</v>
-      </c>
-      <c r="B36" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" t="s">
-        <v>123</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>20330051920040</v>
-      </c>
-      <c r="B37" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" t="s">
-        <v>83</v>
-      </c>
-      <c r="D37" t="s">
-        <v>124</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>20330051920044</v>
-      </c>
-      <c r="B38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" t="s">
-        <v>84</v>
-      </c>
-      <c r="D38" t="s">
-        <v>125</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>20330051920046</v>
-      </c>
-      <c r="B39" t="s">
-        <v>58</v>
-      </c>
-      <c r="C39" t="s">
-        <v>85</v>
-      </c>
-      <c r="D39" t="s">
-        <v>126</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>14</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>20330051920052</v>
-      </c>
-      <c r="B40" t="s">
-        <v>23</v>
-      </c>
-      <c r="C40" t="s">
-        <v>86</v>
-      </c>
-      <c r="D40" t="s">
-        <v>116</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>20330051920096</v>
-      </c>
-      <c r="B41" t="s">
-        <v>49</v>
-      </c>
-      <c r="C41" t="s">
-        <v>87</v>
-      </c>
-      <c r="D41" t="s">
-        <v>127</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>14</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>20330051920104</v>
-      </c>
-      <c r="B42" t="s">
-        <v>59</v>
-      </c>
-      <c r="C42" t="s">
-        <v>66</v>
-      </c>
-      <c r="D42" t="s">
-        <v>128</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>20330051920111</v>
-      </c>
-      <c r="B43" t="s">
-        <v>60</v>
-      </c>
-      <c r="C43" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" t="s">
-        <v>129</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="120">
   <si>
     <t>Mat</t>
   </si>
@@ -103,6 +103,12 @@
     <t>BARRAGAN</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>ARROYO</t>
   </si>
   <si>
@@ -127,57 +133,57 @@
     <t>ZUÑIGA</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CUEVAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
@@ -196,6 +202,12 @@
     <t>VILLALBA</t>
   </si>
   <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>PONCE</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
@@ -214,6 +226,12 @@
     <t>ROBLES</t>
   </si>
   <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -268,6 +286,12 @@
     <t>ADAN</t>
   </si>
   <si>
+    <t>ELIEL</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
     <t>VICTOR HUGO</t>
   </si>
   <si>
@@ -292,61 +316,67 @@
     <t>DANIELA</t>
   </si>
   <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>ALEXA</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>DIANA ARELI</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>EDGAR DANIEL</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAHIR</t>
+  </si>
+  <si>
+    <t>OMAR ALDAIR</t>
+  </si>
+  <si>
+    <t>JAROMI YAJAIRA</t>
+  </si>
+  <si>
+    <t>EDGAR RAMSES</t>
+  </si>
+  <si>
+    <t>XIMENA MICHELL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
     <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
-  </si>
-  <si>
-    <t>OMAR ALDAIR</t>
-  </si>
-  <si>
-    <t>JAROMI YAJAIRA</t>
-  </si>
-  <si>
-    <t>EDGAR RAMSES</t>
-  </si>
-  <si>
-    <t>XIMENA MICHELL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
   </si>
 </sst>
 </file>
@@ -1289,7 +1319,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1327,10 +1357,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1350,10 +1380,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1373,10 +1403,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1396,10 +1426,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1419,10 +1449,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1442,10 +1472,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1459,22 +1489,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920157</v>
+        <v>20330051920345</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1482,22 +1512,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920158</v>
+        <v>20330051920356</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1505,16 +1535,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920164</v>
+        <v>20330051920157</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1528,16 +1558,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920168</v>
+        <v>20330051920158</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1551,16 +1581,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920174</v>
+        <v>20330051920164</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1574,16 +1604,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920178</v>
+        <v>20330051920168</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1597,16 +1627,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920182</v>
+        <v>20330051920174</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1620,16 +1650,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920388</v>
+        <v>20330051920178</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1643,22 +1673,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920112</v>
+        <v>20330051920182</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1666,85 +1696,85 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920362</v>
+        <v>20330051920388</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920011</v>
+        <v>20330051920101</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920012</v>
+        <v>20330051920296</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920060</v>
+        <v>20330051920362</v>
       </c>
       <c r="B20" t="s">
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1758,16 +1788,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920033</v>
+        <v>20330051920011</v>
       </c>
       <c r="B21" t="s">
         <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1781,22 +1811,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920340</v>
+        <v>20330051920012</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1804,22 +1834,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920381</v>
+        <v>20330051920060</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1827,22 +1857,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920347</v>
+        <v>20330051920033</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D24" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1850,16 +1880,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920349</v>
+        <v>20330051920340</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -1873,16 +1903,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>19330050470596</v>
+        <v>20330051920381</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -1896,22 +1926,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920180</v>
+        <v>20330051920347</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1919,22 +1949,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920373</v>
+        <v>20330051920349</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1942,22 +1972,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920145</v>
+        <v>19330050470596</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1965,22 +1995,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920044</v>
+        <v>20330051920180</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D30" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1988,22 +2018,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920046</v>
+        <v>20330051920373</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2011,22 +2041,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920052</v>
+        <v>20330051920145</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2034,16 +2064,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920096</v>
+        <v>20330051920044</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2057,16 +2087,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920097</v>
+        <v>20330051920046</v>
       </c>
       <c r="B34" t="s">
         <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2080,16 +2110,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920104</v>
+        <v>20330051920052</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2098,6 +2128,98 @@
         <v>14</v>
       </c>
       <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>20330051920096</v>
+      </c>
+      <c r="B36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" t="s">
+        <v>116</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>20330051920097</v>
+      </c>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" t="s">
+        <v>117</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>20330051920104</v>
+      </c>
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>20330051920112</v>
+      </c>
+      <c r="B39" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" t="s">
+        <v>71</v>
+      </c>
+      <c r="D39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="122">
   <si>
     <t>Mat</t>
   </si>
@@ -136,6 +136,9 @@
     <t>ORTIZ</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>CORONA</t>
   </si>
   <si>
@@ -320,6 +323,9 @@
   </si>
   <si>
     <t>ALEXA</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
   </si>
   <si>
     <t>JOSUE</t>
@@ -1102,19 +1108,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>84.38</v>
+        <v>90.63</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -1300,16 +1306,16 @@
         <v>1</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>96.88</v>
+        <v>93.75</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1319,7 +1325,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1357,10 +1363,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1380,10 +1386,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1403,10 +1409,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1426,10 +1432,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1449,10 +1455,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1472,10 +1478,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1495,10 +1501,10 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1518,10 +1524,10 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1541,10 +1547,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1564,10 +1570,10 @@
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1587,10 +1593,10 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1610,10 +1616,10 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1633,10 +1639,10 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1656,10 +1662,10 @@
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1679,10 +1685,10 @@
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1702,10 +1708,10 @@
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1725,10 +1731,10 @@
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1748,10 +1754,10 @@
         <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1765,30 +1771,30 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920362</v>
+        <v>20330051920311</v>
       </c>
       <c r="B20" t="s">
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920011</v>
+        <v>20330051920362</v>
       </c>
       <c r="B21" t="s">
         <v>40</v>
@@ -1797,7 +1803,7 @@
         <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1811,16 +1817,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920012</v>
+        <v>20330051920011</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1834,7 +1840,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920060</v>
+        <v>20330051920012</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
@@ -1843,7 +1849,7 @@
         <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1857,16 +1863,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920033</v>
+        <v>20330051920060</v>
       </c>
       <c r="B24" t="s">
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1880,22 +1886,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920340</v>
+        <v>20330051920033</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1903,16 +1909,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920381</v>
+        <v>20330051920340</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
         <v>75</v>
       </c>
       <c r="D26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -1926,16 +1932,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920347</v>
+        <v>20330051920381</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -1949,16 +1955,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920349</v>
+        <v>20330051920347</v>
       </c>
       <c r="B28" t="s">
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -1972,7 +1978,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>19330050470596</v>
+        <v>20330051920349</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
@@ -1981,7 +1987,7 @@
         <v>77</v>
       </c>
       <c r="D29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -1995,22 +2001,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920180</v>
+        <v>19330050470596</v>
       </c>
       <c r="B30" t="s">
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="D30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2018,16 +2024,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920373</v>
+        <v>20330051920180</v>
       </c>
       <c r="B31" t="s">
         <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -2041,16 +2047,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920145</v>
+        <v>20330051920373</v>
       </c>
       <c r="B32" t="s">
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -2064,22 +2070,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920044</v>
+        <v>20330051920145</v>
       </c>
       <c r="B33" t="s">
         <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2087,7 +2093,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920046</v>
+        <v>20330051920044</v>
       </c>
       <c r="B34" t="s">
         <v>51</v>
@@ -2096,7 +2102,7 @@
         <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2110,16 +2116,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920052</v>
+        <v>20330051920046</v>
       </c>
       <c r="B35" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
         <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2133,16 +2139,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>20330051920096</v>
+        <v>20330051920052</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
         <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2156,16 +2162,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>20330051920097</v>
+        <v>20330051920096</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
         <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2179,16 +2185,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>20330051920104</v>
+        <v>20330051920097</v>
       </c>
       <c r="B38" t="s">
         <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2202,16 +2208,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>20330051920112</v>
+        <v>20330051920104</v>
       </c>
       <c r="B39" t="s">
         <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D39" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2220,6 +2226,29 @@
         <v>14</v>
       </c>
       <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>20330051920112</v>
+      </c>
+      <c r="B40" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" t="s">
+        <v>72</v>
+      </c>
+      <c r="D40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
@@ -1004,16 +1004,16 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H3">
         <v>7.9</v>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="116">
   <si>
     <t>Mat</t>
   </si>
@@ -94,72 +94,66 @@
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>MENDOZA</t>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
   </si>
   <si>
     <t>BACILIO</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>CUEVAS</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
     <t>VENTURA</t>
   </si>
   <si>
@@ -196,63 +190,57 @@
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>LEON</t>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
   </si>
   <si>
     <t>ATILANO</t>
   </si>
   <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
     <t>CUATRA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -280,79 +268,73 @@
     <t>OCTAVIO</t>
   </si>
   <si>
-    <t>ITZEL</t>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>ELIEL</t>
+  </si>
+  <si>
+    <t>EDGAR DANIEL</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAHIR</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>AISHA NAOMI</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>ALEXA</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>DIANA ARELI</t>
   </si>
   <si>
     <t>YAIR</t>
   </si>
   <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>ELIEL</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
-  </si>
-  <si>
-    <t>ALEXA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
-  </si>
-  <si>
     <t>CESAR</t>
-  </si>
-  <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
   </si>
   <si>
     <t>OMAR ALDAIR</t>
@@ -1325,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1363,10 +1345,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1386,10 +1368,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1409,10 +1391,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1426,22 +1408,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920241</v>
+        <v>20330051920337</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1449,16 +1431,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920336</v>
+        <v>20330051920345</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1472,16 +1454,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920337</v>
+        <v>20330051920381</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1495,16 +1477,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920345</v>
+        <v>20330051920347</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1518,16 +1500,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920356</v>
+        <v>20330051920349</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1544,13 +1526,13 @@
         <v>20330051920157</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1567,13 +1549,13 @@
         <v>20330051920158</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1590,13 +1572,13 @@
         <v>20330051920164</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1613,13 +1595,13 @@
         <v>20330051920168</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1636,13 +1618,13 @@
         <v>20330051920174</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1659,13 +1641,13 @@
         <v>20330051920178</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1682,13 +1664,13 @@
         <v>20330051920182</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1705,13 +1687,13 @@
         <v>20330051920388</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1728,13 +1710,13 @@
         <v>20330051920101</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1751,13 +1733,13 @@
         <v>20330051920296</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1774,13 +1756,13 @@
         <v>20330051920311</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -1797,13 +1779,13 @@
         <v>20330051920362</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1820,13 +1802,13 @@
         <v>20330051920011</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1843,13 +1825,13 @@
         <v>20330051920012</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1866,13 +1848,13 @@
         <v>20330051920060</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1889,13 +1871,13 @@
         <v>20330051920033</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1909,16 +1891,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920340</v>
+        <v>20330051920336</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -1932,16 +1914,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920381</v>
+        <v>20330051920340</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -1955,16 +1937,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920347</v>
+        <v>19330050470596</v>
       </c>
       <c r="B28" t="s">
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -1978,22 +1960,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920349</v>
+        <v>20330051920180</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2001,22 +1983,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>19330050470596</v>
+        <v>20330051920373</v>
       </c>
       <c r="B30" t="s">
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2024,16 +2006,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920180</v>
+        <v>20330051920145</v>
       </c>
       <c r="B31" t="s">
         <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -2047,22 +2029,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920373</v>
+        <v>20330051920044</v>
       </c>
       <c r="B32" t="s">
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2070,22 +2052,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920145</v>
+        <v>20330051920046</v>
       </c>
       <c r="B33" t="s">
         <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2093,16 +2075,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920044</v>
+        <v>20330051920052</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2116,16 +2098,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920046</v>
+        <v>20330051920096</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2139,16 +2121,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>20330051920052</v>
+        <v>20330051920097</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2162,16 +2144,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>20330051920096</v>
+        <v>20330051920104</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D37" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2185,16 +2167,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>20330051920097</v>
+        <v>20330051920112</v>
       </c>
       <c r="B38" t="s">
         <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D38" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2203,52 +2185,6 @@
         <v>14</v>
       </c>
       <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>20330051920104</v>
-      </c>
-      <c r="B39" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" t="s">
-        <v>78</v>
-      </c>
-      <c r="D39" t="s">
-        <v>120</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>14</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>20330051920112</v>
-      </c>
-      <c r="B40" t="s">
-        <v>55</v>
-      </c>
-      <c r="C40" t="s">
-        <v>72</v>
-      </c>
-      <c r="D40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="90">
   <si>
     <t>Mat</t>
   </si>
@@ -94,123 +94,87 @@
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>CUEVAS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
@@ -223,9 +187,6 @@
     <t>ROSETE</t>
   </si>
   <si>
-    <t>PRADO</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -235,30 +196,24 @@
     <t>VINALAY</t>
   </si>
   <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
+    <t>CHONCOA</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
     <t>CRISTOPHER ALAIN</t>
   </si>
   <si>
@@ -268,30 +223,15 @@
     <t>OCTAVIO</t>
   </si>
   <si>
-    <t>ADAN</t>
-  </si>
-  <si>
     <t>ELIEL</t>
   </si>
   <si>
-    <t>EDGAR DANIEL</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAHIR</t>
-  </si>
-  <si>
     <t>VICTOR HUGO</t>
   </si>
   <si>
     <t>DINA BERENICE</t>
   </si>
   <si>
-    <t>AISHA NAOMI</t>
-  </si>
-  <si>
     <t>ALDAIR OMAR</t>
   </si>
   <si>
@@ -310,9 +250,6 @@
     <t>SERGIO MARIANO</t>
   </si>
   <si>
-    <t>ALEXA</t>
-  </si>
-  <si>
     <t>DULCE MARIA</t>
   </si>
   <si>
@@ -331,28 +268,13 @@
     <t>DIANA ARELI</t>
   </si>
   <si>
-    <t>YAIR</t>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
   </si>
   <si>
     <t>CESAR</t>
-  </si>
-  <si>
-    <t>OMAR ALDAIR</t>
-  </si>
-  <si>
-    <t>JAROMI YAJAIRA</t>
-  </si>
-  <si>
-    <t>EDGAR RAMSES</t>
-  </si>
-  <si>
-    <t>XIMENA MICHELL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
   </si>
   <si>
     <t>ADRIAN</t>
@@ -791,10 +713,10 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>34</v>
@@ -817,19 +739,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>52.38</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -843,19 +765,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>67.56999999999999</v>
+        <v>81.08</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -895,10 +817,10 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>31</v>
@@ -907,7 +829,7 @@
         <v>96.88</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -986,10 +908,10 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>33</v>
@@ -1012,19 +934,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>52.38</v>
+        <v>90.48</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1038,19 +960,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>64.86</v>
+        <v>81.08</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1090,19 +1012,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>90.63</v>
+        <v>96.88</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1181,10 +1103,10 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>33</v>
@@ -1193,7 +1115,7 @@
         <v>94.29000000000001</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1207,19 +1129,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>52.38</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1233,19 +1155,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>67.56999999999999</v>
+        <v>81.08</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1285,19 +1207,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>93.75</v>
+        <v>96.88</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1307,7 +1229,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1345,10 +1267,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1368,10 +1290,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1391,10 +1313,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1408,16 +1330,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920337</v>
+        <v>20330051920345</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1431,22 +1353,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920345</v>
+        <v>20330051920157</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1454,22 +1376,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920381</v>
+        <v>20330051920158</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1477,22 +1399,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920347</v>
+        <v>20330051920168</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1500,22 +1422,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920349</v>
+        <v>20330051920174</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1523,16 +1445,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920157</v>
+        <v>20330051920178</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1546,16 +1468,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920158</v>
+        <v>20330051920182</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1569,16 +1491,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920164</v>
+        <v>20330051920388</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1592,22 +1514,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920168</v>
+        <v>20330051920101</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1615,22 +1537,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920174</v>
+        <v>20330051920311</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1638,160 +1560,160 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920178</v>
+        <v>20330051920362</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920182</v>
+        <v>20330051920011</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920388</v>
+        <v>20330051920012</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920101</v>
+        <v>20330051920060</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920296</v>
+        <v>20330051920033</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920311</v>
+        <v>20330051920044</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920362</v>
+        <v>20330051920046</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1799,22 +1721,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920011</v>
+        <v>20330051920052</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D22" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1822,22 +1744,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920012</v>
+        <v>20330051920096</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1845,22 +1767,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920060</v>
+        <v>20330051920097</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1868,22 +1790,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920033</v>
+        <v>20330051920104</v>
       </c>
       <c r="B25" t="s">
         <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1891,300 +1813,24 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920336</v>
+        <v>20330051920112</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="D26" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920340</v>
-      </c>
-      <c r="B27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" t="s">
-        <v>73</v>
-      </c>
-      <c r="D27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>19330050470596</v>
-      </c>
-      <c r="B28" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" t="s">
-        <v>106</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920180</v>
-      </c>
-      <c r="B29" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" t="s">
-        <v>107</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>20330051920373</v>
-      </c>
-      <c r="B30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" t="s">
-        <v>108</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920145</v>
-      </c>
-      <c r="B31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" t="s">
-        <v>109</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>20330051920044</v>
-      </c>
-      <c r="B32" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" t="s">
-        <v>75</v>
-      </c>
-      <c r="D32" t="s">
-        <v>110</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>20330051920046</v>
-      </c>
-      <c r="B33" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" t="s">
-        <v>76</v>
-      </c>
-      <c r="D33" t="s">
-        <v>111</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>20330051920052</v>
-      </c>
-      <c r="B34" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" t="s">
-        <v>77</v>
-      </c>
-      <c r="D34" t="s">
-        <v>105</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>20330051920096</v>
-      </c>
-      <c r="B35" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" t="s">
-        <v>112</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>20330051920097</v>
-      </c>
-      <c r="B36" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" t="s">
-        <v>79</v>
-      </c>
-      <c r="D36" t="s">
-        <v>113</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>20330051920104</v>
-      </c>
-      <c r="B37" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" t="s">
-        <v>114</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>20330051920112</v>
-      </c>
-      <c r="B38" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" t="s">
-        <v>69</v>
-      </c>
-      <c r="D38" t="s">
-        <v>115</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
@@ -109,48 +109,48 @@
     <t>NAMORADO</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>QUIRIZ</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
@@ -175,27 +175,27 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
     <t>CHONCOA</t>
   </si>
   <si>
@@ -238,55 +238,55 @@
     <t>LUZ ESTRELLA</t>
   </si>
   <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>DIANA ARELI</t>
+  </si>
+  <si>
     <t>MONICA</t>
   </si>
   <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
   </si>
   <si>
     <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
   </si>
 </sst>
 </file>
@@ -1445,7 +1445,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920178</v>
+        <v>20330051920182</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
@@ -1468,7 +1468,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920182</v>
+        <v>20330051920388</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920388</v>
+        <v>20330051920101</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
@@ -1503,10 +1503,10 @@
         <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920101</v>
+        <v>20330051920362</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
@@ -1529,41 +1529,41 @@
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920311</v>
+        <v>20330051920011</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
         <v>77</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920362</v>
+        <v>20330051920012</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
         <v>56</v>
@@ -1583,10 +1583,10 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920011</v>
+        <v>20330051920060</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
         <v>57</v>
@@ -1606,13 +1606,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920012</v>
+        <v>20330051920033</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
         <v>80</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920060</v>
+        <v>20330051920178</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
@@ -1641,10 +1641,10 @@
         <v>81</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1652,13 +1652,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920033</v>
+        <v>20330051920044</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
         <v>82</v>
@@ -1667,7 +1667,7 @@
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1675,13 +1675,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920044</v>
+        <v>20330051920046</v>
       </c>
       <c r="B20" t="s">
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
         <v>83</v>
@@ -1698,13 +1698,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920046</v>
+        <v>20330051920052</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
         <v>84</v>
@@ -1721,13 +1721,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920052</v>
+        <v>20330051920096</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
         <v>85</v>
@@ -1744,13 +1744,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920096</v>
+        <v>20330051920097</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
         <v>86</v>
@@ -1767,13 +1767,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920097</v>
+        <v>20330051920104</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
         <v>87</v>
@@ -1790,13 +1790,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920104</v>
+        <v>20330051920112</v>
       </c>
       <c r="B25" t="s">
         <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s">
         <v>88</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920112</v>
+        <v>20330051920311</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
         <v>89</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26">
         <v>1</v>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="93">
   <si>
     <t>Mat</t>
   </si>
@@ -67,6 +67,9 @@
     <t>5BLCM</t>
   </si>
   <si>
+    <t>5APV</t>
+  </si>
+  <si>
     <t>NC</t>
   </si>
   <si>
@@ -97,6 +100,9 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>ARROYO</t>
   </si>
   <si>
@@ -163,6 +169,9 @@
     <t>IXTLA</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
@@ -193,9 +202,6 @@
     <t>VINALAY</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>CHONCOA</t>
   </si>
   <si>
@@ -224,6 +230,9 @@
   </si>
   <si>
     <t>ELIEL</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
   </si>
   <si>
     <t>VICTOR HUGO</t>
@@ -644,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -832,6 +841,32 @@
         <v>7.5</v>
       </c>
     </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>68.42</v>
+      </c>
+      <c r="H8">
+        <v>6.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -839,7 +874,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1027,6 +1062,32 @@
         <v>7.5</v>
       </c>
     </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>78.95</v>
+      </c>
+      <c r="H8">
+        <v>6.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1034,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1222,6 +1283,32 @@
         <v>7.9</v>
       </c>
     </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>78.95</v>
+      </c>
+      <c r="H8">
+        <v>7.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1229,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1238,25 +1325,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1264,13 +1351,13 @@
         <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1287,13 +1374,13 @@
         <v>20330051920013</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1310,13 +1397,13 @@
         <v>20330051920021</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1333,13 +1420,13 @@
         <v>20330051920345</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1353,22 +1440,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920157</v>
+        <v>20330051920278</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1376,16 +1463,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920158</v>
+        <v>20330051920157</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1399,16 +1486,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920168</v>
+        <v>20330051920158</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1422,16 +1509,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920174</v>
+        <v>20330051920168</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1445,16 +1532,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920182</v>
+        <v>20330051920174</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1468,16 +1555,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920388</v>
+        <v>20330051920182</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1491,22 +1578,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920101</v>
+        <v>20330051920388</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1514,39 +1601,39 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920362</v>
+        <v>20330051920101</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920011</v>
+        <v>20330051920362</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1560,16 +1647,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920012</v>
+        <v>20330051920011</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1583,16 +1670,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920060</v>
+        <v>20330051920012</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1606,16 +1693,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920033</v>
+        <v>20330051920060</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1629,22 +1716,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920178</v>
+        <v>20330051920033</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1652,22 +1739,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920044</v>
+        <v>20330051920178</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1675,16 +1762,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920046</v>
+        <v>20330051920044</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1698,16 +1785,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920052</v>
+        <v>20330051920046</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1721,16 +1808,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920096</v>
+        <v>20330051920052</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1744,16 +1831,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920097</v>
+        <v>20330051920096</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1767,16 +1854,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920104</v>
+        <v>20330051920097</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1790,16 +1877,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920112</v>
+        <v>20330051920104</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1813,24 +1900,47 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
+        <v>20330051920112</v>
+      </c>
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
         <v>20330051920311</v>
       </c>
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" t="s">
-        <v>89</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
         <v>15</v>
       </c>
-      <c r="G26">
+      <c r="G27">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
@@ -97,45 +97,45 @@
     <t>MAZAHUA</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>QUIRIZ</t>
   </si>
   <si>
@@ -166,42 +166,42 @@
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
     <t>IXTLA</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
     <t>CHONCOA</t>
   </si>
   <si>
@@ -229,46 +229,46 @@
     <t>OCTAVIO</t>
   </si>
   <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>DINA BERENICE</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>DIANA ARELI</t>
+  </si>
+  <si>
     <t>ELIEL</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
   </si>
   <si>
     <t>MONICA</t>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920345</v>
+        <v>20330051920278</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -1429,10 +1429,10 @@
         <v>70</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1440,7 +1440,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920278</v>
+        <v>20330051920157</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
@@ -1452,10 +1452,10 @@
         <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920157</v>
+        <v>20330051920158</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920158</v>
+        <v>20330051920168</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
@@ -1509,7 +1509,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920168</v>
+        <v>20330051920174</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
@@ -1532,7 +1532,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920174</v>
+        <v>20330051920182</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -1555,7 +1555,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920182</v>
+        <v>20330051920388</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920388</v>
+        <v>20330051920101</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
@@ -1590,10 +1590,10 @@
         <v>77</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1601,7 +1601,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920101</v>
+        <v>20330051920362</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
@@ -1616,15 +1616,15 @@
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920362</v>
+        <v>20330051920011</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
@@ -1647,13 +1647,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920011</v>
+        <v>20330051920012</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
         <v>80</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920012</v>
+        <v>20330051920060</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
@@ -1693,13 +1693,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920060</v>
+        <v>20330051920033</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
         <v>82</v>
@@ -1716,22 +1716,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920033</v>
+        <v>20330051920345</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
         <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1745,7 +1745,7 @@
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
         <v>84</v>
@@ -1834,7 +1834,7 @@
         <v>20330051920096</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
         <v>64</v>
@@ -1906,7 +1906,7 @@
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s">
         <v>91</v>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="77">
   <si>
     <t>Mat</t>
   </si>
@@ -88,63 +88,48 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>ADELL</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
   </si>
   <si>
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -157,51 +142,36 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>JUAREZ</t>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
   </si>
   <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
     <t>VINALAY</t>
   </si>
   <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
     <t>CHONCOA</t>
   </si>
   <si>
@@ -220,58 +190,40 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
     <t>CRISTOPHER ALAIN</t>
   </si>
   <si>
-    <t>LUIS ANGEL</t>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
   </si>
   <si>
     <t>OCTAVIO</t>
   </si>
   <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>DINA BERENICE</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
     <t>ANGEL SAID</t>
   </si>
   <si>
     <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>ELIEL</t>
-  </si>
-  <si>
-    <t>MONICA</t>
   </si>
   <si>
     <t>URIEL</t>
@@ -1167,16 +1119,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1193,16 +1145,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>95.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1219,16 +1171,16 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>81.08</v>
+        <v>94.59</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1316,7 +1268,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1348,16 +1300,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920002</v>
+        <v>20330051920013</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1371,22 +1323,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920013</v>
+        <v>20330051920278</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1394,22 +1346,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920021</v>
+        <v>20330051920168</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1417,22 +1369,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920278</v>
+        <v>20330051920182</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1440,22 +1392,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920157</v>
+        <v>20330051920101</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1463,154 +1415,154 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920158</v>
+        <v>20330051920002</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920168</v>
+        <v>20330051920362</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920174</v>
+        <v>20330051920011</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920182</v>
+        <v>20330051920012</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920388</v>
+        <v>20330051920021</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920101</v>
+        <v>20330051920060</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920362</v>
+        <v>20330051920033</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1624,22 +1576,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920011</v>
+        <v>20330051920044</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1647,22 +1599,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920012</v>
+        <v>20330051920046</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1670,22 +1622,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920060</v>
+        <v>20330051920052</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1693,22 +1645,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920033</v>
+        <v>20330051920096</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1716,22 +1668,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920345</v>
+        <v>20330051920097</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1739,22 +1691,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920178</v>
+        <v>20330051920104</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1762,16 +1714,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920044</v>
+        <v>20330051920112</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1785,162 +1737,24 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920046</v>
+        <v>20330051920311</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920052</v>
-      </c>
-      <c r="B22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920096</v>
-      </c>
-      <c r="B23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920097</v>
-      </c>
-      <c r="B24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" t="s">
-        <v>89</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920104</v>
-      </c>
-      <c r="B25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" t="s">
-        <v>90</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920112</v>
-      </c>
-      <c r="B26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" t="s">
-        <v>91</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920311</v>
-      </c>
-      <c r="B27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" t="s">
-        <v>92</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="76">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,9 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
@@ -100,7 +103,7 @@
     <t>TORRES</t>
   </si>
   <si>
-    <t>ORTIZ</t>
+    <t>VASQUEZ</t>
   </si>
   <si>
     <t>ADELL</t>
@@ -136,9 +139,6 @@
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
@@ -154,15 +154,12 @@
     <t>MELO</t>
   </si>
   <si>
-    <t>ROSETE</t>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>TEQUIHUATLE</t>
   </si>
   <si>
@@ -193,6 +190,9 @@
     <t>LUIS ANGEL</t>
   </si>
   <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
     <t>MARCO JOSAFAT</t>
   </si>
   <si>
@@ -202,7 +202,7 @@
     <t>DIEGO</t>
   </si>
   <si>
-    <t>SERGIO MARIANO</t>
+    <t>GUILLERMO</t>
   </si>
   <si>
     <t>CRISTOPHER ALAIN</t>
@@ -242,9 +242,6 @@
   </si>
   <si>
     <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
   </si>
   <si>
     <t>DULCE MARIA</t>
@@ -1309,7 +1306,7 @@
         <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1323,16 +1320,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920278</v>
+        <v>19330051920314</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1346,22 +1343,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920168</v>
+        <v>20330051920278</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1369,16 +1366,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920182</v>
+        <v>20330051920168</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1392,22 +1389,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920101</v>
+        <v>20330051920182</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1415,39 +1412,39 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920002</v>
+        <v>20330051920112</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920362</v>
+        <v>20330051920002</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1461,16 +1458,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920011</v>
+        <v>20330051920362</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1484,16 +1481,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920012</v>
+        <v>20330051920011</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1507,16 +1504,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920021</v>
+        <v>20330051920012</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1530,16 +1527,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920060</v>
+        <v>20330051920021</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1553,16 +1550,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920033</v>
+        <v>20330051920060</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1576,22 +1573,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920044</v>
+        <v>20330051920033</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1599,16 +1596,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920046</v>
+        <v>20330051920044</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1622,16 +1619,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920052</v>
+        <v>20330051920046</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1645,16 +1642,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920096</v>
+        <v>20330051920052</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1668,16 +1665,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920097</v>
+        <v>20330051920096</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1691,16 +1688,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920104</v>
+        <v>20330051920097</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1714,16 +1711,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920112</v>
+        <v>20330051920104</v>
       </c>
       <c r="B20" t="s">
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1746,7 +1743,7 @@
         <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="79">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,9 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
@@ -103,7 +106,7 @@
     <t>TORRES</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
+    <t>VALENTE</t>
   </si>
   <si>
     <t>ADELL</t>
@@ -118,78 +121,84 @@
     <t>MAZAHUA</t>
   </si>
   <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>CHONCOA</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
+    <t>MARCOS URIEL</t>
+  </si>
+  <si>
     <t>JOSE ANTONIO</t>
   </si>
   <si>
@@ -202,7 +211,7 @@
     <t>DIEGO</t>
   </si>
   <si>
-    <t>GUILLERMO</t>
+    <t>ABIUD</t>
   </si>
   <si>
     <t>CRISTOPHER ALAIN</t>
@@ -220,28 +229,28 @@
     <t>OCTAVIO</t>
   </si>
   <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>JOSE ABRAHAM</t>
+  </si>
+  <si>
     <t>ANGEL SAID</t>
   </si>
   <si>
+    <t>JOSE MATEO</t>
+  </si>
+  <si>
     <t>DIANA ARELI</t>
   </si>
   <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
+    <t>CRISTAL</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
   </si>
   <si>
     <t>DULCE MARIA</t>
@@ -1090,16 +1099,16 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>70.97</v>
+        <v>58.06</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1194,13 +1203,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>63.33</v>
+        <v>76.67</v>
       </c>
       <c r="H6">
         <v>6.4</v>
@@ -1255,7 +1264,7 @@
         <v>78.95</v>
       </c>
       <c r="H8">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1265,7 +1274,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1303,10 +1312,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1320,22 +1329,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920314</v>
+        <v>20330051920035</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1343,16 +1352,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920278</v>
+        <v>19330051920314</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1366,22 +1375,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920168</v>
+        <v>20330051920278</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1389,16 +1398,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920182</v>
+        <v>20330051920168</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1412,22 +1421,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920112</v>
+        <v>20330051920182</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1435,39 +1444,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920002</v>
+        <v>20330051920111</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920362</v>
+        <v>20330051920002</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1481,16 +1490,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920011</v>
+        <v>20330051920362</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1504,16 +1513,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920012</v>
+        <v>20330051920011</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1527,16 +1536,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920021</v>
+        <v>20330051920012</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1550,16 +1559,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920060</v>
+        <v>20330051920021</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1573,16 +1582,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920033</v>
+        <v>20330051920025</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1596,22 +1605,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920044</v>
+        <v>20330051920026</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1619,22 +1628,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920046</v>
+        <v>20330051920060</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1642,22 +1651,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920052</v>
+        <v>20330051920029</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1665,22 +1674,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920096</v>
+        <v>20330051920033</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1688,22 +1697,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920097</v>
+        <v>20330051920037</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1711,16 +1720,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920104</v>
+        <v>20330051920040</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1734,24 +1743,47 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
+        <v>20330051920050</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
         <v>20330051920311</v>
       </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" t="s">
         <v>9</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F22" t="s">
         <v>15</v>
       </c>
-      <c r="G21">
+      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
+++ b/docentes/Duran Amezcua María Angélica - Estadisticos 20221.xlsx
@@ -103,48 +103,48 @@
     <t>HUESCA</t>
   </si>
   <si>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>VALENTE</t>
   </si>
   <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
@@ -160,39 +160,39 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
     <t>MELO</t>
   </si>
   <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
     <t>GAMEZ</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>VINALAY</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
@@ -208,49 +208,49 @@
     <t>ALDAIR OMAR</t>
   </si>
   <si>
+    <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>JOSE ABRAHAM</t>
+  </si>
+  <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>JOSE MATEO</t>
+  </si>
+  <si>
+    <t>DIANA ARELI</t>
+  </si>
+  <si>
+    <t>CRISTAL</t>
+  </si>
+  <si>
     <t>DIEGO</t>
   </si>
   <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
     <t>ABIUD</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ALAIN</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>OCTAVIO</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>JOSE ABRAHAM</t>
-  </si>
-  <si>
-    <t>ANGEL SAID</t>
-  </si>
-  <si>
-    <t>JOSE MATEO</t>
-  </si>
-  <si>
-    <t>DIANA ARELI</t>
-  </si>
-  <si>
-    <t>CRISTAL</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
   </si>
   <si>
     <t>DULCE MARIA</t>
@@ -654,10 +654,10 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>11</v>
@@ -666,7 +666,7 @@
         <v>35.48</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -732,10 +732,10 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5">
         <v>30</v>
@@ -875,10 +875,10 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>22</v>
@@ -887,7 +887,7 @@
         <v>70.97</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -927,16 +927,16 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>90.48</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H4">
         <v>7.9</v>
@@ -953,10 +953,10 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5">
         <v>30</v>
@@ -1031,7 +1031,7 @@
         <v>19</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>4</v>
@@ -1043,7 +1043,7 @@
         <v>78.95</v>
       </c>
       <c r="H8">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -1096,10 +1096,10 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>18</v>
@@ -1108,7 +1108,7 @@
         <v>58.06</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1151,16 +1151,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1174,10 +1174,10 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>35</v>
@@ -1186,7 +1186,7 @@
         <v>94.59</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1421,7 +1421,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920182</v>
+        <v>20330051920002</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
@@ -1433,24 +1433,24 @@
         <v>63</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920111</v>
+        <v>20330051920362</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
         <v>64</v>
@@ -1459,21 +1459,21 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920002</v>
+        <v>20330051920011</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
         <v>65</v>
@@ -1490,13 +1490,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920362</v>
+        <v>20330051920012</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
         <v>66</v>
@@ -1513,13 +1513,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920011</v>
+        <v>20330051920021</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
         <v>67</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920012</v>
+        <v>20330051920025</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
@@ -1559,7 +1559,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920021</v>
+        <v>20330051920026</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
@@ -1582,7 +1582,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920025</v>
+        <v>20330051920060</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920026</v>
+        <v>20330051920029</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
@@ -1628,13 +1628,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920060</v>
+        <v>20330051920033</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
         <v>72</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920029</v>
+        <v>20330051920037</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
         <v>73</v>
@@ -1674,22 +1674,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920033</v>
+        <v>20330051920182</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
         <v>74</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1697,7 +1697,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920037</v>
+        <v>20330051920040</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
@@ -1712,7 +1712,7 @@
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1720,13 +1720,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920040</v>
+        <v>20330051920050</v>
       </c>
       <c r="B20" t="s">
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
         <v>76</v>
@@ -1743,13 +1743,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920050</v>
+        <v>20330051920111</v>
       </c>
       <c r="B21" t="s">
         <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
         <v>77</v>
